--- a/artifacts/aura-forecast/public/exports/Training_Audit_Report.xlsx
+++ b/artifacts/aura-forecast/public/exports/Training_Audit_Report.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Training_Audit" sheetId="1" r:id="rId1"/>
+    <sheet name="Analysis_Charts" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -47,7 +48,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Exact source dataset</t>
+          <t>Analysis dataset</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -152,15 +153,202 @@
         </is>
       </c>
     </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Analysis item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Training rows</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>202965</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Validation rows</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>58217</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Holdout rows</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>74021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Leakage check</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Visual asset</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_missingness.svg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Missing percentage by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_outliers.svg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Flagged outlier counts by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>analytics/hist_temperature.svg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Temperature histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>analytics/hist_pressure.svg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pressure histogram</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Date conversion</t>
+          <t>analytics/hist_refractivity.svg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The observation dates were calendar-shifted from 2022 to 2026 for the project's forecasting timeline while preserving the original month, day and time structure.</t>
+          <t>Refractivity histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>analytics/correlation_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Predictor correlation with refractivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>analytics/daily_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Daily refractivity trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>analytics/monthly_forecast.svg</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Monthly forecast comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>analytics/validation_metrics.svg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chronological validation scorecard</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>analytics/training_holdout_rows.svg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Training, holdout, and validation counts</t>
         </is>
       </c>
     </row>
